--- a/reports/pdf_rolling5_20261001.xlsx
+++ b/reports/pdf_rolling5_20261001.xlsx
@@ -560,7 +560,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,035억   ·   현금 40억(0.8%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 15종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,035억   ·   현금 20억(0.4%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 15종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1177,88 +1177,88 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>224369818</v>
+        <v>1049352820</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>4.52%→5.13%</t>
+          <t>1.83%→2.05%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>568→573</t>
+          <t>44→49</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-633838593</v>
+        <v>-296079690</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.49%</t>
+          <t>1.04%→0.91%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1049352820</v>
+        <v>224369818</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.83%→2.05%</t>
+          <t>4.52%→5.13%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>44→49</t>
+          <t>568→573</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-296079690</v>
+        <v>-633838593</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.91%</t>
+          <t>0.65%→0.49%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,250억   ·   현금 76억(2.3%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 3종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,250억   ·   현금 38억(1.2%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1570,7 +1570,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,723억   ·   현금 86억(3.1%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,723억   ·   현금 43억(1.6%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1594,7 +1594,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,988억   ·   현금 19억(1.0%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 7종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,988억   ·   현금 9억(0.5%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 7종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1959,7 +1959,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 308억   ·   현금 3억(0.9%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 8종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 308억   ·   현금 1억(0.5%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 8종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -2456,7 +2456,7 @@
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 474억   ·   현금 15억(3.1%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 1종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 474억   ·   현금 8억(1.6%)      오늘 2026-10-01  vs  5일전 2026-09-22      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B59" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261001.xlsx
+++ b/reports/pdf_rolling5_20261001.xlsx
@@ -2405,23 +2405,23 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-70434000</v>
+        <v>-34314000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.98%→2.75%</t>
+          <t>1.49%→1.38%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-34314000</v>
+        <v>-70434000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.49%→1.38%</t>
+          <t>2.98%→2.75%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261001.xlsx
+++ b/reports/pdf_rolling5_20261001.xlsx
@@ -1110,23 +1110,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-862877663</v>
+        <v>-2751909340</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.47%</t>
+          <t>2.61%→1.90%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -1154,46 +1154,46 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-2751909340</v>
+        <v>-862877663</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2.61%→1.90%</t>
+          <t>0.70%→0.47%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1049352820</v>
+        <v>224369818</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.83%→2.05%</t>
+          <t>4.52%→5.13%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>44→49</t>
+          <t>568→573</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1221,23 +1221,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>224369818</v>
+        <v>1049352820</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>4.52%→5.13%</t>
+          <t>1.83%→2.05%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>568→573</t>
+          <t>44→49</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261001.xlsx
+++ b/reports/pdf_rolling5_20261001.xlsx
@@ -1198,23 +1198,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-296079690</v>
+        <v>-633838593</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.91%</t>
+          <t>0.65%→0.49%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -1242,23 +1242,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-633838593</v>
+        <v>-296079690</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.49%</t>
+          <t>1.04%→0.91%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
@@ -2377,23 +2377,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-63126000</v>
+        <v>-70434000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2.78%→2.57%</t>
+          <t>2.98%→2.75%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>
@@ -2405,23 +2405,23 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-34314000</v>
+        <v>-63126000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>1.49%→1.38%</t>
+          <t>2.78%→2.57%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-70434000</v>
+        <v>-34314000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.98%→2.75%</t>
+          <t>1.49%→1.38%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261001.xlsx
+++ b/reports/pdf_rolling5_20261001.xlsx
@@ -1110,23 +1110,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2751909340</v>
+        <v>-862877663</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>2.61%→1.90%</t>
+          <t>0.70%→0.47%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
@@ -1154,23 +1154,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-862877663</v>
+        <v>-2751909340</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.47%</t>
+          <t>2.61%→1.90%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -1198,23 +1198,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-633838593</v>
+        <v>-296079690</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.49%</t>
+          <t>1.04%→0.91%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
@@ -1242,23 +1242,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-296079690</v>
+        <v>-633838593</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.91%</t>
+          <t>0.65%→0.49%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -2377,23 +2377,23 @@
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-70434000</v>
+        <v>-63126000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>2.98%→2.75%</t>
+          <t>2.78%→2.57%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>78→72</t>
+          <t>81→75</t>
         </is>
       </c>
     </row>
@@ -2405,23 +2405,23 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-63126000</v>
+        <v>-34314000</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.78%→2.57%</t>
+          <t>1.49%→1.38%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>81→75</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -2433,23 +2433,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-34314000</v>
+        <v>-70434000</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.49%→1.38%</t>
+          <t>2.98%→2.75%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>78→72</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261001.xlsx
+++ b/reports/pdf_rolling5_20261001.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +62,13 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +100,11 @@
         <fgColor rgb="00E4ECF6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -122,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -162,6 +172,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -553,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-22 ~ 2026-10-01  (최근 5거래일)  ·  캡처 7/7</t>
+          <t>최근 5거래일 변화  ·  2026-09-22 ~ 2026-10-01  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1110,23 +1124,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-862877663</v>
+        <v>-2751909340</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.70%→0.47%</t>
+          <t>2.61%→1.90%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>41→30</t>
+          <t>49→38</t>
         </is>
       </c>
     </row>
@@ -1154,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-2751909340</v>
+        <v>-862877663</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>2.61%→1.90%</t>
+          <t>0.70%→0.47%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>49→38</t>
+          <t>41→30</t>
         </is>
       </c>
     </row>
@@ -1198,23 +1212,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-296079690</v>
+        <v>-633838593</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.91%</t>
+          <t>0.65%→0.49%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>131→123</t>
+          <t>39→31</t>
         </is>
       </c>
     </row>
@@ -1242,23 +1256,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-633838593</v>
+        <v>-296079690</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.49%</t>
+          <t>1.04%→0.91%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>39→31</t>
+          <t>131→123</t>
         </is>
       </c>
     </row>
@@ -2615,31 +2629,24 @@
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,133억      오늘 2026-10-01  vs  5일전 2026-09-22      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="n"/>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="20" t="n"/>
+      <c r="E65" s="20" t="n"/>
+      <c r="F65" s="20" t="n"/>
+      <c r="G65" s="20" t="n"/>
+      <c r="H65" s="20" t="n"/>
+      <c r="I65" s="20" t="n"/>
+      <c r="J65" s="20" t="n"/>
+      <c r="K65" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A59:K59"/>
     <mergeCell ref="A60:E60"/>
@@ -2649,7 +2656,6 @@
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A65:K65"/>
     <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A66:K66"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A32:K32"/>
